--- a/dataset/randomized_and_labeled_WK.xlsx
+++ b/dataset/randomized_and_labeled_WK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/w_kooijman_uu_nl/Documents/Updated place holder/[Place holder]/Students/Lukas Vaartjes/final_dataset/dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lukas\Documents\GitHub\master_thesis_public\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2893" documentId="11_529563EC87534F1EC92D4C94CD6E30B57877A1F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5468510E-14D9-4B73-ACB8-555D1182FEE2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C7CF34-5567-482C-A921-3ECD5F4EA178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
